--- a/artfynd/A 14070-2022 artfynd.xlsx
+++ b/artfynd/A 14070-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14070-2022 artfynd.xlsx
+++ b/artfynd/A 14070-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88020940</v>
+        <v>88020941</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skalmodal, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478825.8582649093</v>
+        <v>478833</v>
       </c>
       <c r="R2" t="n">
-        <v>7257811.028754515</v>
+        <v>7257824</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +752,9 @@
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,131 +778,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>88020941</v>
-      </c>
-      <c r="B3" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Skalmodal, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>478833.0337913806</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7257823.876734005</v>
-      </c>
-      <c r="S3" t="n">
-        <v>25</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
